--- a/templates/tpl_booking_mssnhsjl9u3s.xlsx
+++ b/templates/tpl_booking_mssnhsjl9u3s.xlsx
@@ -415,266 +415,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="522.1428571428571" customWidth="1" min="1" max="1"/>
-    <col width="574.2857142857143" customWidth="1" min="2" max="2"/>
-    <col width="491" customWidth="1" min="3" max="3"/>
-    <col width="464.5714285714286" customWidth="1" min="4" max="4"/>
-    <col width="720.5714285714286" customWidth="1" min="5" max="5"/>
-    <col width="887.8571428571429" customWidth="1" min="6" max="6"/>
-    <col width="658.2857142857143" customWidth="1" min="7" max="7"/>
-    <col width="1091.714285714286" customWidth="1" min="8" max="8"/>
-    <col width="585.1428571428571" customWidth="1" min="9" max="9"/>
-    <col width="459.4285714285714" customWidth="1" min="10" max="10"/>
-    <col width="459.4285714285714" customWidth="1" min="11" max="11"/>
-    <col width="459.4285714285714" customWidth="1" min="12" max="12"/>
-    <col width="459.4285714285714" customWidth="1" min="13" max="13"/>
-    <col width="459.4285714285714" customWidth="1" min="14" max="14"/>
-    <col width="459.4285714285714" customWidth="1" min="15" max="15"/>
-    <col width="459.4285714285714" customWidth="1" min="16" max="16"/>
-    <col width="459.4285714285714" customWidth="1" min="17" max="17"/>
-    <col width="459.4285714285714" customWidth="1" min="18" max="18"/>
-    <col width="459.4285714285714" customWidth="1" min="19" max="19"/>
-    <col width="459.4285714285714" customWidth="1" min="20" max="20"/>
-    <col width="459.4285714285714" customWidth="1" min="21" max="21"/>
-    <col width="459.4285714285714" customWidth="1" min="22" max="22"/>
-    <col width="459.4285714285714" customWidth="1" min="23" max="23"/>
-    <col width="459.4285714285714" customWidth="1" min="24" max="24"/>
-    <col width="459.4285714285714" customWidth="1" min="25" max="25"/>
-    <col width="459.4285714285714" customWidth="1" min="26" max="26"/>
-    <col width="459.4285714285714" customWidth="1" min="27" max="27"/>
-    <col width="459.4285714285714" customWidth="1" min="28" max="28"/>
-    <col width="459.4285714285714" customWidth="1" min="29" max="29"/>
-    <col width="459.4285714285714" customWidth="1" min="30" max="30"/>
-    <col width="459.4285714285714" customWidth="1" min="31" max="31"/>
-    <col width="459.4285714285714" customWidth="1" min="32" max="32"/>
-    <col width="459.4285714285714" customWidth="1" min="33" max="33"/>
-    <col width="459.4285714285714" customWidth="1" min="34" max="34"/>
-    <col width="459.4285714285714" customWidth="1" min="35" max="35"/>
-    <col width="459.4285714285714" customWidth="1" min="36" max="36"/>
-    <col width="459.4285714285714" customWidth="1" min="37" max="37"/>
-    <col width="459.4285714285714" customWidth="1" min="38" max="38"/>
-    <col width="459.4285714285714" customWidth="1" min="39" max="39"/>
-    <col width="459.4285714285714" customWidth="1" min="40" max="40"/>
-    <col width="459.4285714285714" customWidth="1" min="41" max="41"/>
-    <col width="459.4285714285714" customWidth="1" min="42" max="42"/>
-    <col width="459.4285714285714" customWidth="1" min="43" max="43"/>
-    <col width="459.4285714285714" customWidth="1" min="44" max="44"/>
-    <col width="459.4285714285714" customWidth="1" min="45" max="45"/>
-    <col width="459.4285714285714" customWidth="1" min="46" max="46"/>
-    <col width="459.4285714285714" customWidth="1" min="47" max="47"/>
-    <col width="459.4285714285714" customWidth="1" min="48" max="48"/>
-    <col width="459.4285714285714" customWidth="1" min="49" max="49"/>
-    <col width="459.4285714285714" customWidth="1" min="50" max="50"/>
-    <col width="459.4285714285714" customWidth="1" min="51" max="51"/>
-    <col width="459.4285714285714" customWidth="1" min="52" max="52"/>
-    <col width="459.4285714285714" customWidth="1" min="53" max="53"/>
-    <col width="459.4285714285714" customWidth="1" min="54" max="54"/>
-    <col width="459.4285714285714" customWidth="1" min="55" max="55"/>
-    <col width="459.4285714285714" customWidth="1" min="56" max="56"/>
-    <col width="459.4285714285714" customWidth="1" min="57" max="57"/>
-    <col width="459.4285714285714" customWidth="1" min="58" max="58"/>
-    <col width="459.4285714285714" customWidth="1" min="59" max="59"/>
-    <col width="459.4285714285714" customWidth="1" min="60" max="60"/>
-    <col width="459.4285714285714" customWidth="1" min="61" max="61"/>
-    <col width="459.4285714285714" customWidth="1" min="62" max="62"/>
-    <col width="459.4285714285714" customWidth="1" min="63" max="63"/>
-    <col width="459.4285714285714" customWidth="1" min="64" max="64"/>
-    <col width="459.4285714285714" customWidth="1" min="65" max="65"/>
-    <col width="459.4285714285714" customWidth="1" min="66" max="66"/>
-    <col width="459.4285714285714" customWidth="1" min="67" max="67"/>
-    <col width="459.4285714285714" customWidth="1" min="68" max="68"/>
-    <col width="459.4285714285714" customWidth="1" min="69" max="69"/>
-    <col width="459.4285714285714" customWidth="1" min="70" max="70"/>
-    <col width="459.4285714285714" customWidth="1" min="71" max="71"/>
-    <col width="459.4285714285714" customWidth="1" min="72" max="72"/>
-    <col width="459.4285714285714" customWidth="1" min="73" max="73"/>
-    <col width="459.4285714285714" customWidth="1" min="74" max="74"/>
-    <col width="459.4285714285714" customWidth="1" min="75" max="75"/>
-    <col width="459.4285714285714" customWidth="1" min="76" max="76"/>
-    <col width="459.4285714285714" customWidth="1" min="77" max="77"/>
-    <col width="459.4285714285714" customWidth="1" min="78" max="78"/>
-    <col width="459.4285714285714" customWidth="1" min="79" max="79"/>
-    <col width="459.4285714285714" customWidth="1" min="80" max="80"/>
-    <col width="459.4285714285714" customWidth="1" min="81" max="81"/>
-    <col width="459.4285714285714" customWidth="1" min="82" max="82"/>
-    <col width="459.4285714285714" customWidth="1" min="83" max="83"/>
-    <col width="459.4285714285714" customWidth="1" min="84" max="84"/>
-    <col width="459.4285714285714" customWidth="1" min="85" max="85"/>
-    <col width="459.4285714285714" customWidth="1" min="86" max="86"/>
-    <col width="459.4285714285714" customWidth="1" min="87" max="87"/>
-    <col width="459.4285714285714" customWidth="1" min="88" max="88"/>
-    <col width="459.4285714285714" customWidth="1" min="89" max="89"/>
-    <col width="459.4285714285714" customWidth="1" min="90" max="90"/>
-    <col width="459.4285714285714" customWidth="1" min="91" max="91"/>
-    <col width="459.4285714285714" customWidth="1" min="92" max="92"/>
-    <col width="459.4285714285714" customWidth="1" min="93" max="93"/>
-    <col width="459.4285714285714" customWidth="1" min="94" max="94"/>
-    <col width="459.4285714285714" customWidth="1" min="95" max="95"/>
-    <col width="459.4285714285714" customWidth="1" min="96" max="96"/>
-    <col width="459.4285714285714" customWidth="1" min="97" max="97"/>
-    <col width="459.4285714285714" customWidth="1" min="98" max="98"/>
-    <col width="459.4285714285714" customWidth="1" min="99" max="99"/>
-    <col width="459.4285714285714" customWidth="1" min="100" max="100"/>
-    <col width="459.4285714285714" customWidth="1" min="101" max="101"/>
-    <col width="459.4285714285714" customWidth="1" min="102" max="102"/>
-    <col width="459.4285714285714" customWidth="1" min="103" max="103"/>
-    <col width="459.4285714285714" customWidth="1" min="104" max="104"/>
-    <col width="459.4285714285714" customWidth="1" min="105" max="105"/>
-    <col width="459.4285714285714" customWidth="1" min="106" max="106"/>
-    <col width="459.4285714285714" customWidth="1" min="107" max="107"/>
-    <col width="459.4285714285714" customWidth="1" min="108" max="108"/>
-    <col width="459.4285714285714" customWidth="1" min="109" max="109"/>
-    <col width="459.4285714285714" customWidth="1" min="110" max="110"/>
-    <col width="459.4285714285714" customWidth="1" min="111" max="111"/>
-    <col width="459.4285714285714" customWidth="1" min="112" max="112"/>
-    <col width="459.4285714285714" customWidth="1" min="113" max="113"/>
-    <col width="459.4285714285714" customWidth="1" min="114" max="114"/>
-    <col width="459.4285714285714" customWidth="1" min="115" max="115"/>
-    <col width="459.4285714285714" customWidth="1" min="116" max="116"/>
-    <col width="459.4285714285714" customWidth="1" min="117" max="117"/>
-    <col width="459.4285714285714" customWidth="1" min="118" max="118"/>
-    <col width="459.4285714285714" customWidth="1" min="119" max="119"/>
-    <col width="459.4285714285714" customWidth="1" min="120" max="120"/>
-    <col width="459.4285714285714" customWidth="1" min="121" max="121"/>
-    <col width="459.4285714285714" customWidth="1" min="122" max="122"/>
-    <col width="459.4285714285714" customWidth="1" min="123" max="123"/>
-    <col width="459.4285714285714" customWidth="1" min="124" max="124"/>
-    <col width="459.4285714285714" customWidth="1" min="125" max="125"/>
-    <col width="459.4285714285714" customWidth="1" min="126" max="126"/>
-    <col width="459.4285714285714" customWidth="1" min="127" max="127"/>
-    <col width="459.4285714285714" customWidth="1" min="128" max="128"/>
-    <col width="459.4285714285714" customWidth="1" min="129" max="129"/>
-    <col width="459.4285714285714" customWidth="1" min="130" max="130"/>
-    <col width="459.4285714285714" customWidth="1" min="131" max="131"/>
-    <col width="459.4285714285714" customWidth="1" min="132" max="132"/>
-    <col width="459.4285714285714" customWidth="1" min="133" max="133"/>
-    <col width="459.4285714285714" customWidth="1" min="134" max="134"/>
-    <col width="459.4285714285714" customWidth="1" min="135" max="135"/>
-    <col width="459.4285714285714" customWidth="1" min="136" max="136"/>
-    <col width="459.4285714285714" customWidth="1" min="137" max="137"/>
-    <col width="459.4285714285714" customWidth="1" min="138" max="138"/>
-    <col width="459.4285714285714" customWidth="1" min="139" max="139"/>
-    <col width="459.4285714285714" customWidth="1" min="140" max="140"/>
-    <col width="459.4285714285714" customWidth="1" min="141" max="141"/>
-    <col width="459.4285714285714" customWidth="1" min="142" max="142"/>
-    <col width="459.4285714285714" customWidth="1" min="143" max="143"/>
-    <col width="459.4285714285714" customWidth="1" min="144" max="144"/>
-    <col width="459.4285714285714" customWidth="1" min="145" max="145"/>
-    <col width="459.4285714285714" customWidth="1" min="146" max="146"/>
-    <col width="459.4285714285714" customWidth="1" min="147" max="147"/>
-    <col width="459.4285714285714" customWidth="1" min="148" max="148"/>
-    <col width="459.4285714285714" customWidth="1" min="149" max="149"/>
-    <col width="459.4285714285714" customWidth="1" min="150" max="150"/>
-    <col width="459.4285714285714" customWidth="1" min="151" max="151"/>
-    <col width="459.4285714285714" customWidth="1" min="152" max="152"/>
-    <col width="459.4285714285714" customWidth="1" min="153" max="153"/>
-    <col width="459.4285714285714" customWidth="1" min="154" max="154"/>
-    <col width="459.4285714285714" customWidth="1" min="155" max="155"/>
-    <col width="459.4285714285714" customWidth="1" min="156" max="156"/>
-    <col width="459.4285714285714" customWidth="1" min="157" max="157"/>
-    <col width="459.4285714285714" customWidth="1" min="158" max="158"/>
-    <col width="459.4285714285714" customWidth="1" min="159" max="159"/>
-    <col width="459.4285714285714" customWidth="1" min="160" max="160"/>
-    <col width="459.4285714285714" customWidth="1" min="161" max="161"/>
-    <col width="459.4285714285714" customWidth="1" min="162" max="162"/>
-    <col width="459.4285714285714" customWidth="1" min="163" max="163"/>
-    <col width="459.4285714285714" customWidth="1" min="164" max="164"/>
-    <col width="459.4285714285714" customWidth="1" min="165" max="165"/>
-    <col width="459.4285714285714" customWidth="1" min="166" max="166"/>
-    <col width="459.4285714285714" customWidth="1" min="167" max="167"/>
-    <col width="459.4285714285714" customWidth="1" min="168" max="168"/>
-    <col width="459.4285714285714" customWidth="1" min="169" max="169"/>
-    <col width="459.4285714285714" customWidth="1" min="170" max="170"/>
-    <col width="459.4285714285714" customWidth="1" min="171" max="171"/>
-    <col width="459.4285714285714" customWidth="1" min="172" max="172"/>
-    <col width="459.4285714285714" customWidth="1" min="173" max="173"/>
-    <col width="459.4285714285714" customWidth="1" min="174" max="174"/>
-    <col width="459.4285714285714" customWidth="1" min="175" max="175"/>
-    <col width="459.4285714285714" customWidth="1" min="176" max="176"/>
-    <col width="459.4285714285714" customWidth="1" min="177" max="177"/>
-    <col width="459.4285714285714" customWidth="1" min="178" max="178"/>
-    <col width="459.4285714285714" customWidth="1" min="179" max="179"/>
-    <col width="459.4285714285714" customWidth="1" min="180" max="180"/>
-    <col width="459.4285714285714" customWidth="1" min="181" max="181"/>
-    <col width="459.4285714285714" customWidth="1" min="182" max="182"/>
-    <col width="459.4285714285714" customWidth="1" min="183" max="183"/>
-    <col width="459.4285714285714" customWidth="1" min="184" max="184"/>
-    <col width="459.4285714285714" customWidth="1" min="185" max="185"/>
-    <col width="459.4285714285714" customWidth="1" min="186" max="186"/>
-    <col width="459.4285714285714" customWidth="1" min="187" max="187"/>
-    <col width="459.4285714285714" customWidth="1" min="188" max="188"/>
-    <col width="459.4285714285714" customWidth="1" min="189" max="189"/>
-    <col width="459.4285714285714" customWidth="1" min="190" max="190"/>
-    <col width="459.4285714285714" customWidth="1" min="191" max="191"/>
-    <col width="459.4285714285714" customWidth="1" min="192" max="192"/>
-    <col width="459.4285714285714" customWidth="1" min="193" max="193"/>
-    <col width="459.4285714285714" customWidth="1" min="194" max="194"/>
-    <col width="459.4285714285714" customWidth="1" min="195" max="195"/>
-    <col width="459.4285714285714" customWidth="1" min="196" max="196"/>
-    <col width="459.4285714285714" customWidth="1" min="197" max="197"/>
-    <col width="459.4285714285714" customWidth="1" min="198" max="198"/>
-    <col width="459.4285714285714" customWidth="1" min="199" max="199"/>
-    <col width="459.4285714285714" customWidth="1" min="200" max="200"/>
-    <col width="459.4285714285714" customWidth="1" min="201" max="201"/>
-    <col width="459.4285714285714" customWidth="1" min="202" max="202"/>
-    <col width="459.4285714285714" customWidth="1" min="203" max="203"/>
-    <col width="459.4285714285714" customWidth="1" min="204" max="204"/>
-    <col width="459.4285714285714" customWidth="1" min="205" max="205"/>
-    <col width="459.4285714285714" customWidth="1" min="206" max="206"/>
-    <col width="459.4285714285714" customWidth="1" min="207" max="207"/>
-    <col width="459.4285714285714" customWidth="1" min="208" max="208"/>
-    <col width="459.4285714285714" customWidth="1" min="209" max="209"/>
-    <col width="459.4285714285714" customWidth="1" min="210" max="210"/>
-    <col width="459.4285714285714" customWidth="1" min="211" max="211"/>
-    <col width="459.4285714285714" customWidth="1" min="212" max="212"/>
-    <col width="459.4285714285714" customWidth="1" min="213" max="213"/>
-    <col width="459.4285714285714" customWidth="1" min="214" max="214"/>
-    <col width="459.4285714285714" customWidth="1" min="215" max="215"/>
-    <col width="459.4285714285714" customWidth="1" min="216" max="216"/>
-    <col width="459.4285714285714" customWidth="1" min="217" max="217"/>
-    <col width="459.4285714285714" customWidth="1" min="218" max="218"/>
-    <col width="459.4285714285714" customWidth="1" min="219" max="219"/>
-    <col width="459.4285714285714" customWidth="1" min="220" max="220"/>
-    <col width="459.4285714285714" customWidth="1" min="221" max="221"/>
-    <col width="459.4285714285714" customWidth="1" min="222" max="222"/>
-    <col width="459.4285714285714" customWidth="1" min="223" max="223"/>
-    <col width="459.4285714285714" customWidth="1" min="224" max="224"/>
-    <col width="459.4285714285714" customWidth="1" min="225" max="225"/>
-    <col width="459.4285714285714" customWidth="1" min="226" max="226"/>
-    <col width="459.4285714285714" customWidth="1" min="227" max="227"/>
-    <col width="459.4285714285714" customWidth="1" min="228" max="228"/>
-    <col width="459.4285714285714" customWidth="1" min="229" max="229"/>
-    <col width="459.4285714285714" customWidth="1" min="230" max="230"/>
-    <col width="459.4285714285714" customWidth="1" min="231" max="231"/>
-    <col width="459.4285714285714" customWidth="1" min="232" max="232"/>
-    <col width="459.4285714285714" customWidth="1" min="233" max="233"/>
-    <col width="459.4285714285714" customWidth="1" min="234" max="234"/>
-    <col width="459.4285714285714" customWidth="1" min="235" max="235"/>
-    <col width="459.4285714285714" customWidth="1" min="236" max="236"/>
-    <col width="459.4285714285714" customWidth="1" min="237" max="237"/>
-    <col width="459.4285714285714" customWidth="1" min="238" max="238"/>
-    <col width="459.4285714285714" customWidth="1" min="239" max="239"/>
-    <col width="459.4285714285714" customWidth="1" min="240" max="240"/>
-    <col width="459.4285714285714" customWidth="1" min="241" max="241"/>
-    <col width="459.4285714285714" customWidth="1" min="242" max="242"/>
-    <col width="459.4285714285714" customWidth="1" min="243" max="243"/>
-    <col width="459.4285714285714" customWidth="1" min="244" max="244"/>
-    <col width="459.4285714285714" customWidth="1" min="245" max="245"/>
-    <col width="459.4285714285714" customWidth="1" min="246" max="246"/>
-    <col width="459.4285714285714" customWidth="1" min="247" max="247"/>
-    <col width="459.4285714285714" customWidth="1" min="248" max="248"/>
-    <col width="407.2857142857143" customWidth="1" min="249" max="249"/>
-    <col width="375.8571428571428" customWidth="1" min="250" max="250"/>
-    <col width="464.5714285714286" customWidth="1" min="251" max="251"/>
-    <col width="595.2857142857143" customWidth="1" min="252" max="252"/>
-    <col width="647.4285714285714" customWidth="1" min="253" max="253"/>
-    <col width="574.2857142857143" customWidth="1" min="254" max="254"/>
-    <col width="470" customWidth="1" min="255" max="255"/>
-    <col width="470" customWidth="1" min="256" max="256"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -682,6 +424,13 @@
           <t>C.H. Robinson Freight Services (China) Ltd. Shenzhen Branch</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -689,11 +438,17 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>1601 Building E, Baoneng Center, No.3008 Baoan North Road, Luohu District</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,6 +456,13 @@
           <t>Shenzhen China. Tel:86-755-82185777 Fax:86-755-82185111</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -708,27 +470,52 @@
           <t>Shipper (Full Name &amp; Address) 发货人：</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Payment Term 运杂费付款安排</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Freight Term 运费付款方式</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Trade Term 贸易条款</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">Service Mode     </t>
@@ -746,6 +533,12 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>CFS/CFS</t>
@@ -763,25 +556,44 @@
           <t>Manufacturer (Full Name &amp; Address) 制造商:</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Cargo Ready Date 预计可出货日期：</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">No. of Containers (For CY/CY Only) 柜型及数量: </t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>________ x20'GP</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>________x40'GP</t>
@@ -789,11 +601,17 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>________   x40'HQ</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>________x45'</t>
@@ -806,27 +624,55 @@
           <t>Consignee (Full Name &amp; Address) 收货人(货权所有人）：</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>BL Type</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>提单类型</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Payer Company Name 出货方付款公司抬头:                     非SHIPPER的抬头时请提供中文+英文</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -834,6 +680,13 @@
           <t>US Registered Code: (ex. IRS/EIN/SSN)</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -841,11 +694,17 @@
           <t xml:space="preserve">RFC: CMO101104D21 </t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Currency 付款币种：</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -853,36 +712,106 @@
           <t>Notify Party (Full Name &amp; Address) 通知人：</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Shipping Order</t>
         </is>
       </c>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>Also Notify party:(if any) 第二通知人(如有)：</t>
         </is>
       </c>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+    </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t xml:space="preserve">Intended Vsl &amp; Voy </t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Place of Receipt</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">Port of Loading </t>
@@ -905,11 +834,14 @@
           <t>预定船名航次</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>出口收货地（城市）</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>起运地装货港</t>
@@ -927,13 +859,29 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-    </row>
-    <row r="30"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+    </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -950,6 +898,9 @@
           <t>Description of Goods （简短的材质&amp;物名，仅供订仓参考）</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>G.W. (Kgs)</t>
@@ -977,6 +928,9 @@
           <t xml:space="preserve">品名 </t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>总毛重 (公斤）</t>
@@ -987,6 +941,66 @@
           <t>总体积（立方米）</t>
         </is>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -994,6 +1008,13 @@
           <t>是否有实木包装：</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1001,6 +1022,13 @@
           <t>Is it wooden package?</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1008,6 +1036,13 @@
           <t>Container Stuffing Location (Name &amp; Adress)               货柜装载地 （EXW条款时必填项）:</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1015,6 +1050,13 @@
           <t>Consolidator (Stuffer)  (Name &amp; Adress)装柜方 :</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1037,6 +1079,7 @@
           <t xml:space="preserve"> Description</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>Item Q'TY</t>
@@ -1052,6 +1095,126 @@
           <t>Country of Origin</t>
         </is>
       </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1059,6 +1222,13 @@
           <t>Pick-up Arrangements 拖车安排：</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1066,6 +1236,13 @@
           <t>Customs Clearance Arrangements 报关安排：</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1073,6 +1250,23 @@
           <t xml:space="preserve">Special Hanlding Requirement: </t>
         </is>
       </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1080,6 +1274,13 @@
           <t>托运人声明：</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1087,6 +1288,13 @@
           <t>1. 对本委托书所载明之内容的真实性及正确性负责, 并充分了解及接受所列明的相关条款；</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1094,6 +1302,13 @@
           <t>2. 对于运费到付的货物若收货人拒绝付款将依照承运人提单条款执行；</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1101,6 +1316,13 @@
           <t>3. 在货物发生损坏或丢失、可能对承运人提出索赔的情况下，托运人不得扣减或拒付运费及相关费用；</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1108,6 +1330,13 @@
           <t xml:space="preserve">4. 若托运人未按时付款，承运人对于货物及相关单证拥有留置权及依法处理权；  </t>
         </is>
       </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1115,6 +1344,13 @@
           <t>5. 若托运人未按时付款，托运人愿自被通知付款之日起按日息0.1%加付滞纳金。</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1122,13 +1358,36 @@
           <t>6.受托人有权对委托事项进行转委托，并对转委托受托人的过错不承担责任。</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Booking Party's Chop &amp; Authorized Signature</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+    </row>
     <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>CHR-4-ISO-OECS001  A/2</t>
@@ -1136,40 +1395,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="F19:I26"/>
-    <mergeCell ref="H16:I17"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F16:G17"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="E41:I41"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1182,264 +1407,6 @@
   </sheetPr>
   <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="88.71428571428571" customWidth="1" min="1" max="1"/>
-    <col width="914.2857142857143" customWidth="1" min="2" max="2"/>
-    <col width="2105.142857142857" customWidth="1" min="3" max="3"/>
-    <col width="125.2857142857143" customWidth="1" min="4" max="4"/>
-    <col width="88.71428571428571" customWidth="1" min="5" max="5"/>
-    <col width="997.5714285714286" customWidth="1" min="6" max="6"/>
-    <col width="1823.142857142857" customWidth="1" min="7" max="7"/>
-    <col width="329.1428571428572" customWidth="1" min="8" max="8"/>
-    <col width="329.1428571428572" customWidth="1" min="9" max="9"/>
-    <col width="329.1428571428572" customWidth="1" min="10" max="10"/>
-    <col width="329.1428571428572" customWidth="1" min="11" max="11"/>
-    <col width="329.1428571428572" customWidth="1" min="12" max="12"/>
-    <col width="329.1428571428572" customWidth="1" min="13" max="13"/>
-    <col width="329.1428571428572" customWidth="1" min="14" max="14"/>
-    <col width="329.1428571428572" customWidth="1" min="15" max="15"/>
-    <col width="329.1428571428572" customWidth="1" min="16" max="16"/>
-    <col width="329.1428571428572" customWidth="1" min="17" max="17"/>
-    <col width="329.1428571428572" customWidth="1" min="18" max="18"/>
-    <col width="329.1428571428572" customWidth="1" min="19" max="19"/>
-    <col width="329.1428571428572" customWidth="1" min="20" max="20"/>
-    <col width="329.1428571428572" customWidth="1" min="21" max="21"/>
-    <col width="329.1428571428572" customWidth="1" min="22" max="22"/>
-    <col width="329.1428571428572" customWidth="1" min="23" max="23"/>
-    <col width="329.1428571428572" customWidth="1" min="24" max="24"/>
-    <col width="329.1428571428572" customWidth="1" min="25" max="25"/>
-    <col width="329.1428571428572" customWidth="1" min="26" max="26"/>
-    <col width="329.1428571428572" customWidth="1" min="27" max="27"/>
-    <col width="329.1428571428572" customWidth="1" min="28" max="28"/>
-    <col width="329.1428571428572" customWidth="1" min="29" max="29"/>
-    <col width="329.1428571428572" customWidth="1" min="30" max="30"/>
-    <col width="329.1428571428572" customWidth="1" min="31" max="31"/>
-    <col width="329.1428571428572" customWidth="1" min="32" max="32"/>
-    <col width="329.1428571428572" customWidth="1" min="33" max="33"/>
-    <col width="329.1428571428572" customWidth="1" min="34" max="34"/>
-    <col width="329.1428571428572" customWidth="1" min="35" max="35"/>
-    <col width="329.1428571428572" customWidth="1" min="36" max="36"/>
-    <col width="329.1428571428572" customWidth="1" min="37" max="37"/>
-    <col width="329.1428571428572" customWidth="1" min="38" max="38"/>
-    <col width="329.1428571428572" customWidth="1" min="39" max="39"/>
-    <col width="329.1428571428572" customWidth="1" min="40" max="40"/>
-    <col width="329.1428571428572" customWidth="1" min="41" max="41"/>
-    <col width="329.1428571428572" customWidth="1" min="42" max="42"/>
-    <col width="329.1428571428572" customWidth="1" min="43" max="43"/>
-    <col width="329.1428571428572" customWidth="1" min="44" max="44"/>
-    <col width="329.1428571428572" customWidth="1" min="45" max="45"/>
-    <col width="329.1428571428572" customWidth="1" min="46" max="46"/>
-    <col width="329.1428571428572" customWidth="1" min="47" max="47"/>
-    <col width="329.1428571428572" customWidth="1" min="48" max="48"/>
-    <col width="329.1428571428572" customWidth="1" min="49" max="49"/>
-    <col width="329.1428571428572" customWidth="1" min="50" max="50"/>
-    <col width="329.1428571428572" customWidth="1" min="51" max="51"/>
-    <col width="329.1428571428572" customWidth="1" min="52" max="52"/>
-    <col width="329.1428571428572" customWidth="1" min="53" max="53"/>
-    <col width="329.1428571428572" customWidth="1" min="54" max="54"/>
-    <col width="329.1428571428572" customWidth="1" min="55" max="55"/>
-    <col width="329.1428571428572" customWidth="1" min="56" max="56"/>
-    <col width="329.1428571428572" customWidth="1" min="57" max="57"/>
-    <col width="329.1428571428572" customWidth="1" min="58" max="58"/>
-    <col width="329.1428571428572" customWidth="1" min="59" max="59"/>
-    <col width="329.1428571428572" customWidth="1" min="60" max="60"/>
-    <col width="329.1428571428572" customWidth="1" min="61" max="61"/>
-    <col width="329.1428571428572" customWidth="1" min="62" max="62"/>
-    <col width="329.1428571428572" customWidth="1" min="63" max="63"/>
-    <col width="329.1428571428572" customWidth="1" min="64" max="64"/>
-    <col width="329.1428571428572" customWidth="1" min="65" max="65"/>
-    <col width="329.1428571428572" customWidth="1" min="66" max="66"/>
-    <col width="329.1428571428572" customWidth="1" min="67" max="67"/>
-    <col width="329.1428571428572" customWidth="1" min="68" max="68"/>
-    <col width="329.1428571428572" customWidth="1" min="69" max="69"/>
-    <col width="329.1428571428572" customWidth="1" min="70" max="70"/>
-    <col width="329.1428571428572" customWidth="1" min="71" max="71"/>
-    <col width="329.1428571428572" customWidth="1" min="72" max="72"/>
-    <col width="329.1428571428572" customWidth="1" min="73" max="73"/>
-    <col width="329.1428571428572" customWidth="1" min="74" max="74"/>
-    <col width="329.1428571428572" customWidth="1" min="75" max="75"/>
-    <col width="329.1428571428572" customWidth="1" min="76" max="76"/>
-    <col width="329.1428571428572" customWidth="1" min="77" max="77"/>
-    <col width="329.1428571428572" customWidth="1" min="78" max="78"/>
-    <col width="329.1428571428572" customWidth="1" min="79" max="79"/>
-    <col width="329.1428571428572" customWidth="1" min="80" max="80"/>
-    <col width="329.1428571428572" customWidth="1" min="81" max="81"/>
-    <col width="329.1428571428572" customWidth="1" min="82" max="82"/>
-    <col width="329.1428571428572" customWidth="1" min="83" max="83"/>
-    <col width="329.1428571428572" customWidth="1" min="84" max="84"/>
-    <col width="329.1428571428572" customWidth="1" min="85" max="85"/>
-    <col width="329.1428571428572" customWidth="1" min="86" max="86"/>
-    <col width="329.1428571428572" customWidth="1" min="87" max="87"/>
-    <col width="329.1428571428572" customWidth="1" min="88" max="88"/>
-    <col width="329.1428571428572" customWidth="1" min="89" max="89"/>
-    <col width="329.1428571428572" customWidth="1" min="90" max="90"/>
-    <col width="329.1428571428572" customWidth="1" min="91" max="91"/>
-    <col width="329.1428571428572" customWidth="1" min="92" max="92"/>
-    <col width="329.1428571428572" customWidth="1" min="93" max="93"/>
-    <col width="329.1428571428572" customWidth="1" min="94" max="94"/>
-    <col width="329.1428571428572" customWidth="1" min="95" max="95"/>
-    <col width="329.1428571428572" customWidth="1" min="96" max="96"/>
-    <col width="329.1428571428572" customWidth="1" min="97" max="97"/>
-    <col width="329.1428571428572" customWidth="1" min="98" max="98"/>
-    <col width="329.1428571428572" customWidth="1" min="99" max="99"/>
-    <col width="329.1428571428572" customWidth="1" min="100" max="100"/>
-    <col width="329.1428571428572" customWidth="1" min="101" max="101"/>
-    <col width="329.1428571428572" customWidth="1" min="102" max="102"/>
-    <col width="329.1428571428572" customWidth="1" min="103" max="103"/>
-    <col width="329.1428571428572" customWidth="1" min="104" max="104"/>
-    <col width="329.1428571428572" customWidth="1" min="105" max="105"/>
-    <col width="329.1428571428572" customWidth="1" min="106" max="106"/>
-    <col width="329.1428571428572" customWidth="1" min="107" max="107"/>
-    <col width="329.1428571428572" customWidth="1" min="108" max="108"/>
-    <col width="329.1428571428572" customWidth="1" min="109" max="109"/>
-    <col width="329.1428571428572" customWidth="1" min="110" max="110"/>
-    <col width="329.1428571428572" customWidth="1" min="111" max="111"/>
-    <col width="329.1428571428572" customWidth="1" min="112" max="112"/>
-    <col width="329.1428571428572" customWidth="1" min="113" max="113"/>
-    <col width="329.1428571428572" customWidth="1" min="114" max="114"/>
-    <col width="329.1428571428572" customWidth="1" min="115" max="115"/>
-    <col width="329.1428571428572" customWidth="1" min="116" max="116"/>
-    <col width="329.1428571428572" customWidth="1" min="117" max="117"/>
-    <col width="329.1428571428572" customWidth="1" min="118" max="118"/>
-    <col width="329.1428571428572" customWidth="1" min="119" max="119"/>
-    <col width="329.1428571428572" customWidth="1" min="120" max="120"/>
-    <col width="329.1428571428572" customWidth="1" min="121" max="121"/>
-    <col width="329.1428571428572" customWidth="1" min="122" max="122"/>
-    <col width="329.1428571428572" customWidth="1" min="123" max="123"/>
-    <col width="329.1428571428572" customWidth="1" min="124" max="124"/>
-    <col width="329.1428571428572" customWidth="1" min="125" max="125"/>
-    <col width="329.1428571428572" customWidth="1" min="126" max="126"/>
-    <col width="329.1428571428572" customWidth="1" min="127" max="127"/>
-    <col width="329.1428571428572" customWidth="1" min="128" max="128"/>
-    <col width="329.1428571428572" customWidth="1" min="129" max="129"/>
-    <col width="329.1428571428572" customWidth="1" min="130" max="130"/>
-    <col width="329.1428571428572" customWidth="1" min="131" max="131"/>
-    <col width="329.1428571428572" customWidth="1" min="132" max="132"/>
-    <col width="329.1428571428572" customWidth="1" min="133" max="133"/>
-    <col width="329.1428571428572" customWidth="1" min="134" max="134"/>
-    <col width="329.1428571428572" customWidth="1" min="135" max="135"/>
-    <col width="329.1428571428572" customWidth="1" min="136" max="136"/>
-    <col width="329.1428571428572" customWidth="1" min="137" max="137"/>
-    <col width="329.1428571428572" customWidth="1" min="138" max="138"/>
-    <col width="329.1428571428572" customWidth="1" min="139" max="139"/>
-    <col width="329.1428571428572" customWidth="1" min="140" max="140"/>
-    <col width="329.1428571428572" customWidth="1" min="141" max="141"/>
-    <col width="329.1428571428572" customWidth="1" min="142" max="142"/>
-    <col width="329.1428571428572" customWidth="1" min="143" max="143"/>
-    <col width="329.1428571428572" customWidth="1" min="144" max="144"/>
-    <col width="329.1428571428572" customWidth="1" min="145" max="145"/>
-    <col width="329.1428571428572" customWidth="1" min="146" max="146"/>
-    <col width="329.1428571428572" customWidth="1" min="147" max="147"/>
-    <col width="329.1428571428572" customWidth="1" min="148" max="148"/>
-    <col width="329.1428571428572" customWidth="1" min="149" max="149"/>
-    <col width="329.1428571428572" customWidth="1" min="150" max="150"/>
-    <col width="329.1428571428572" customWidth="1" min="151" max="151"/>
-    <col width="329.1428571428572" customWidth="1" min="152" max="152"/>
-    <col width="329.1428571428572" customWidth="1" min="153" max="153"/>
-    <col width="329.1428571428572" customWidth="1" min="154" max="154"/>
-    <col width="329.1428571428572" customWidth="1" min="155" max="155"/>
-    <col width="329.1428571428572" customWidth="1" min="156" max="156"/>
-    <col width="329.1428571428572" customWidth="1" min="157" max="157"/>
-    <col width="329.1428571428572" customWidth="1" min="158" max="158"/>
-    <col width="329.1428571428572" customWidth="1" min="159" max="159"/>
-    <col width="329.1428571428572" customWidth="1" min="160" max="160"/>
-    <col width="329.1428571428572" customWidth="1" min="161" max="161"/>
-    <col width="329.1428571428572" customWidth="1" min="162" max="162"/>
-    <col width="329.1428571428572" customWidth="1" min="163" max="163"/>
-    <col width="329.1428571428572" customWidth="1" min="164" max="164"/>
-    <col width="329.1428571428572" customWidth="1" min="165" max="165"/>
-    <col width="329.1428571428572" customWidth="1" min="166" max="166"/>
-    <col width="329.1428571428572" customWidth="1" min="167" max="167"/>
-    <col width="329.1428571428572" customWidth="1" min="168" max="168"/>
-    <col width="329.1428571428572" customWidth="1" min="169" max="169"/>
-    <col width="329.1428571428572" customWidth="1" min="170" max="170"/>
-    <col width="329.1428571428572" customWidth="1" min="171" max="171"/>
-    <col width="329.1428571428572" customWidth="1" min="172" max="172"/>
-    <col width="329.1428571428572" customWidth="1" min="173" max="173"/>
-    <col width="329.1428571428572" customWidth="1" min="174" max="174"/>
-    <col width="329.1428571428572" customWidth="1" min="175" max="175"/>
-    <col width="329.1428571428572" customWidth="1" min="176" max="176"/>
-    <col width="329.1428571428572" customWidth="1" min="177" max="177"/>
-    <col width="329.1428571428572" customWidth="1" min="178" max="178"/>
-    <col width="329.1428571428572" customWidth="1" min="179" max="179"/>
-    <col width="329.1428571428572" customWidth="1" min="180" max="180"/>
-    <col width="329.1428571428572" customWidth="1" min="181" max="181"/>
-    <col width="329.1428571428572" customWidth="1" min="182" max="182"/>
-    <col width="329.1428571428572" customWidth="1" min="183" max="183"/>
-    <col width="329.1428571428572" customWidth="1" min="184" max="184"/>
-    <col width="329.1428571428572" customWidth="1" min="185" max="185"/>
-    <col width="329.1428571428572" customWidth="1" min="186" max="186"/>
-    <col width="329.1428571428572" customWidth="1" min="187" max="187"/>
-    <col width="329.1428571428572" customWidth="1" min="188" max="188"/>
-    <col width="329.1428571428572" customWidth="1" min="189" max="189"/>
-    <col width="329.1428571428572" customWidth="1" min="190" max="190"/>
-    <col width="329.1428571428572" customWidth="1" min="191" max="191"/>
-    <col width="329.1428571428572" customWidth="1" min="192" max="192"/>
-    <col width="329.1428571428572" customWidth="1" min="193" max="193"/>
-    <col width="329.1428571428572" customWidth="1" min="194" max="194"/>
-    <col width="329.1428571428572" customWidth="1" min="195" max="195"/>
-    <col width="329.1428571428572" customWidth="1" min="196" max="196"/>
-    <col width="329.1428571428572" customWidth="1" min="197" max="197"/>
-    <col width="329.1428571428572" customWidth="1" min="198" max="198"/>
-    <col width="329.1428571428572" customWidth="1" min="199" max="199"/>
-    <col width="329.1428571428572" customWidth="1" min="200" max="200"/>
-    <col width="329.1428571428572" customWidth="1" min="201" max="201"/>
-    <col width="329.1428571428572" customWidth="1" min="202" max="202"/>
-    <col width="329.1428571428572" customWidth="1" min="203" max="203"/>
-    <col width="329.1428571428572" customWidth="1" min="204" max="204"/>
-    <col width="329.1428571428572" customWidth="1" min="205" max="205"/>
-    <col width="329.1428571428572" customWidth="1" min="206" max="206"/>
-    <col width="329.1428571428572" customWidth="1" min="207" max="207"/>
-    <col width="329.1428571428572" customWidth="1" min="208" max="208"/>
-    <col width="329.1428571428572" customWidth="1" min="209" max="209"/>
-    <col width="329.1428571428572" customWidth="1" min="210" max="210"/>
-    <col width="329.1428571428572" customWidth="1" min="211" max="211"/>
-    <col width="329.1428571428572" customWidth="1" min="212" max="212"/>
-    <col width="329.1428571428572" customWidth="1" min="213" max="213"/>
-    <col width="329.1428571428572" customWidth="1" min="214" max="214"/>
-    <col width="329.1428571428572" customWidth="1" min="215" max="215"/>
-    <col width="329.1428571428572" customWidth="1" min="216" max="216"/>
-    <col width="329.1428571428572" customWidth="1" min="217" max="217"/>
-    <col width="329.1428571428572" customWidth="1" min="218" max="218"/>
-    <col width="329.1428571428572" customWidth="1" min="219" max="219"/>
-    <col width="329.1428571428572" customWidth="1" min="220" max="220"/>
-    <col width="329.1428571428572" customWidth="1" min="221" max="221"/>
-    <col width="329.1428571428572" customWidth="1" min="222" max="222"/>
-    <col width="329.1428571428572" customWidth="1" min="223" max="223"/>
-    <col width="329.1428571428572" customWidth="1" min="224" max="224"/>
-    <col width="329.1428571428572" customWidth="1" min="225" max="225"/>
-    <col width="329.1428571428572" customWidth="1" min="226" max="226"/>
-    <col width="329.1428571428572" customWidth="1" min="227" max="227"/>
-    <col width="329.1428571428572" customWidth="1" min="228" max="228"/>
-    <col width="329.1428571428572" customWidth="1" min="229" max="229"/>
-    <col width="329.1428571428572" customWidth="1" min="230" max="230"/>
-    <col width="329.1428571428572" customWidth="1" min="231" max="231"/>
-    <col width="329.1428571428572" customWidth="1" min="232" max="232"/>
-    <col width="329.1428571428572" customWidth="1" min="233" max="233"/>
-    <col width="329.1428571428572" customWidth="1" min="234" max="234"/>
-    <col width="329.1428571428572" customWidth="1" min="235" max="235"/>
-    <col width="329.1428571428572" customWidth="1" min="236" max="236"/>
-    <col width="329.1428571428572" customWidth="1" min="237" max="237"/>
-    <col width="329.1428571428572" customWidth="1" min="238" max="238"/>
-    <col width="329.1428571428572" customWidth="1" min="239" max="239"/>
-    <col width="329.1428571428572" customWidth="1" min="240" max="240"/>
-    <col width="329.1428571428572" customWidth="1" min="241" max="241"/>
-    <col width="329.1428571428572" customWidth="1" min="242" max="242"/>
-    <col width="329.1428571428572" customWidth="1" min="243" max="243"/>
-    <col width="329.1428571428572" customWidth="1" min="244" max="244"/>
-    <col width="329.1428571428572" customWidth="1" min="245" max="245"/>
-    <col width="329.1428571428572" customWidth="1" min="246" max="246"/>
-    <col width="329.1428571428572" customWidth="1" min="247" max="247"/>
-    <col width="329.1428571428572" customWidth="1" min="248" max="248"/>
-    <col width="329.1428571428572" customWidth="1" min="249" max="249"/>
-    <col width="329.1428571428572" customWidth="1" min="250" max="250"/>
-    <col width="329.1428571428572" customWidth="1" min="251" max="251"/>
-    <col width="329.1428571428572" customWidth="1" min="252" max="252"/>
-    <col width="329.1428571428572" customWidth="1" min="253" max="253"/>
-    <col width="329.1428571428572" customWidth="1" min="254" max="254"/>
-    <col width="329.1428571428572" customWidth="1" min="255" max="255"/>
-    <col width="329.1428571428572" customWidth="1" min="256" max="256"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1447,6 +1414,12 @@
           <t>Importer Security Filing (ISF) / Required Elements Worksheet</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1462,6 +1435,7 @@
           <t>The name and address of the supplier of the finished goods in the country from which the goods are leaving. 此项必须填写</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>1a.</t>
@@ -1479,71 +1453,102 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>(Identified to the Item # level if different from the shipper.)</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>Street Address:</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>(Mandatory for textile and FDA shipments.)</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>City:</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>Postal Code:</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Street Address:</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">Country: </t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>City:</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Postal Code:</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,25 +1564,37 @@
           <t>The last known entity by whom the goods are sold or agreed to be sold. 此项必须填写</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">Country: </t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Street Address:</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>3</v>
       </c>
@@ -1593,47 +1610,68 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>City:</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>Postal Code:</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Street Address:</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Country:</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>City:</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Postal Code:</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1649,25 +1687,37 @@
           <t>The first delivery to party scheduled to physically receive the goods after the goods have been released from customs custody. 此项必须填写</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">Country: </t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Street Address:</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>5</v>
       </c>
@@ -1683,47 +1733,68 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>City:</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Postal Code:</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Street Address:</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t xml:space="preserve">Country: </t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>City:</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Postal Code:</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1739,25 +1810,37 @@
           <t>The party who stuffed the container or arranged for the stuffing of the container. 此项整柜必须填写，散货无需填写</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Country: </t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Street Address:</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>8</v>
       </c>
@@ -1773,37 +1856,60 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>City:</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>Postal Code:</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t xml:space="preserve">Country: </t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>IRS, Custom Assigned Number:</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>EIN or Social Security Number:</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1819,20 +1925,37 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>(Please complete only one of the above)</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>Importer of bond number:</t>
         </is>
       </c>
-    </row>
-    <row r="32"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
     <row r="33">
       <c r="A33" t="n">
         <v>9</v>
@@ -1855,6 +1978,7 @@
           <t>Commodity HTSUS number(s):</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Harmonized number(s) to be provided to the 6 digit level. 此项必须填写</t>
@@ -1862,96 +1986,145 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>(Identified to the HTS # level)</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>(Identified to the Item # level.)</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>Country:</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Number:</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>Country:</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Number:</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>Country:</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Number:</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>Country:</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Number:</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>Country:</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Number:</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>Country:</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Number:</t>
         </is>
       </c>
-    </row>
-    <row r="41"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
           <t>Shipping Details (Only House Bill of Lading is required)</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1959,11 +2132,16 @@
           <t>Vessel/Voyage:</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>House Bill of Lading #:</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1971,11 +2149,16 @@
           <t>ETD:</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>Container #:</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1983,6 +2166,12 @@
           <t>ETA:</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1990,11 +2179,16 @@
           <t>Master Bill of Lading #:</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>PO #:</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2002,38 +2196,14 @@
           <t xml:space="preserve">A commercial invoice attached to this document must be received 96 hours prior to sailing to ensure timely filing of 10+2.  These documents should be sent via e-mail to CHR/HK.  The subject line on the email must read Importer of Record Name and bill of lading number (ie.  ABC Importer, CHSL8720006201 ) </t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A42:G42"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2044,266 +2214,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="1029" customWidth="1" min="1" max="1"/>
-    <col width="684" customWidth="1" min="2" max="2"/>
-    <col width="297.5714285714286" customWidth="1" min="3" max="3"/>
-    <col width="684" customWidth="1" min="4" max="4"/>
-    <col width="297.5714285714286" customWidth="1" min="5" max="5"/>
-    <col width="684" customWidth="1" min="6" max="6"/>
-    <col width="329.1428571428572" customWidth="1" min="7" max="7"/>
-    <col width="329.1428571428572" customWidth="1" min="8" max="8"/>
-    <col width="329.1428571428572" customWidth="1" min="9" max="9"/>
-    <col width="329.1428571428572" customWidth="1" min="10" max="10"/>
-    <col width="329.1428571428572" customWidth="1" min="11" max="11"/>
-    <col width="329.1428571428572" customWidth="1" min="12" max="12"/>
-    <col width="329.1428571428572" customWidth="1" min="13" max="13"/>
-    <col width="329.1428571428572" customWidth="1" min="14" max="14"/>
-    <col width="329.1428571428572" customWidth="1" min="15" max="15"/>
-    <col width="329.1428571428572" customWidth="1" min="16" max="16"/>
-    <col width="329.1428571428572" customWidth="1" min="17" max="17"/>
-    <col width="329.1428571428572" customWidth="1" min="18" max="18"/>
-    <col width="329.1428571428572" customWidth="1" min="19" max="19"/>
-    <col width="329.1428571428572" customWidth="1" min="20" max="20"/>
-    <col width="329.1428571428572" customWidth="1" min="21" max="21"/>
-    <col width="329.1428571428572" customWidth="1" min="22" max="22"/>
-    <col width="329.1428571428572" customWidth="1" min="23" max="23"/>
-    <col width="329.1428571428572" customWidth="1" min="24" max="24"/>
-    <col width="329.1428571428572" customWidth="1" min="25" max="25"/>
-    <col width="329.1428571428572" customWidth="1" min="26" max="26"/>
-    <col width="329.1428571428572" customWidth="1" min="27" max="27"/>
-    <col width="329.1428571428572" customWidth="1" min="28" max="28"/>
-    <col width="329.1428571428572" customWidth="1" min="29" max="29"/>
-    <col width="329.1428571428572" customWidth="1" min="30" max="30"/>
-    <col width="329.1428571428572" customWidth="1" min="31" max="31"/>
-    <col width="329.1428571428572" customWidth="1" min="32" max="32"/>
-    <col width="329.1428571428572" customWidth="1" min="33" max="33"/>
-    <col width="329.1428571428572" customWidth="1" min="34" max="34"/>
-    <col width="329.1428571428572" customWidth="1" min="35" max="35"/>
-    <col width="329.1428571428572" customWidth="1" min="36" max="36"/>
-    <col width="329.1428571428572" customWidth="1" min="37" max="37"/>
-    <col width="329.1428571428572" customWidth="1" min="38" max="38"/>
-    <col width="329.1428571428572" customWidth="1" min="39" max="39"/>
-    <col width="329.1428571428572" customWidth="1" min="40" max="40"/>
-    <col width="329.1428571428572" customWidth="1" min="41" max="41"/>
-    <col width="329.1428571428572" customWidth="1" min="42" max="42"/>
-    <col width="329.1428571428572" customWidth="1" min="43" max="43"/>
-    <col width="329.1428571428572" customWidth="1" min="44" max="44"/>
-    <col width="329.1428571428572" customWidth="1" min="45" max="45"/>
-    <col width="329.1428571428572" customWidth="1" min="46" max="46"/>
-    <col width="329.1428571428572" customWidth="1" min="47" max="47"/>
-    <col width="329.1428571428572" customWidth="1" min="48" max="48"/>
-    <col width="329.1428571428572" customWidth="1" min="49" max="49"/>
-    <col width="329.1428571428572" customWidth="1" min="50" max="50"/>
-    <col width="329.1428571428572" customWidth="1" min="51" max="51"/>
-    <col width="329.1428571428572" customWidth="1" min="52" max="52"/>
-    <col width="329.1428571428572" customWidth="1" min="53" max="53"/>
-    <col width="329.1428571428572" customWidth="1" min="54" max="54"/>
-    <col width="329.1428571428572" customWidth="1" min="55" max="55"/>
-    <col width="329.1428571428572" customWidth="1" min="56" max="56"/>
-    <col width="329.1428571428572" customWidth="1" min="57" max="57"/>
-    <col width="329.1428571428572" customWidth="1" min="58" max="58"/>
-    <col width="329.1428571428572" customWidth="1" min="59" max="59"/>
-    <col width="329.1428571428572" customWidth="1" min="60" max="60"/>
-    <col width="329.1428571428572" customWidth="1" min="61" max="61"/>
-    <col width="329.1428571428572" customWidth="1" min="62" max="62"/>
-    <col width="329.1428571428572" customWidth="1" min="63" max="63"/>
-    <col width="329.1428571428572" customWidth="1" min="64" max="64"/>
-    <col width="329.1428571428572" customWidth="1" min="65" max="65"/>
-    <col width="329.1428571428572" customWidth="1" min="66" max="66"/>
-    <col width="329.1428571428572" customWidth="1" min="67" max="67"/>
-    <col width="329.1428571428572" customWidth="1" min="68" max="68"/>
-    <col width="329.1428571428572" customWidth="1" min="69" max="69"/>
-    <col width="329.1428571428572" customWidth="1" min="70" max="70"/>
-    <col width="329.1428571428572" customWidth="1" min="71" max="71"/>
-    <col width="329.1428571428572" customWidth="1" min="72" max="72"/>
-    <col width="329.1428571428572" customWidth="1" min="73" max="73"/>
-    <col width="329.1428571428572" customWidth="1" min="74" max="74"/>
-    <col width="329.1428571428572" customWidth="1" min="75" max="75"/>
-    <col width="329.1428571428572" customWidth="1" min="76" max="76"/>
-    <col width="329.1428571428572" customWidth="1" min="77" max="77"/>
-    <col width="329.1428571428572" customWidth="1" min="78" max="78"/>
-    <col width="329.1428571428572" customWidth="1" min="79" max="79"/>
-    <col width="329.1428571428572" customWidth="1" min="80" max="80"/>
-    <col width="329.1428571428572" customWidth="1" min="81" max="81"/>
-    <col width="329.1428571428572" customWidth="1" min="82" max="82"/>
-    <col width="329.1428571428572" customWidth="1" min="83" max="83"/>
-    <col width="329.1428571428572" customWidth="1" min="84" max="84"/>
-    <col width="329.1428571428572" customWidth="1" min="85" max="85"/>
-    <col width="329.1428571428572" customWidth="1" min="86" max="86"/>
-    <col width="329.1428571428572" customWidth="1" min="87" max="87"/>
-    <col width="329.1428571428572" customWidth="1" min="88" max="88"/>
-    <col width="329.1428571428572" customWidth="1" min="89" max="89"/>
-    <col width="329.1428571428572" customWidth="1" min="90" max="90"/>
-    <col width="329.1428571428572" customWidth="1" min="91" max="91"/>
-    <col width="329.1428571428572" customWidth="1" min="92" max="92"/>
-    <col width="329.1428571428572" customWidth="1" min="93" max="93"/>
-    <col width="329.1428571428572" customWidth="1" min="94" max="94"/>
-    <col width="329.1428571428572" customWidth="1" min="95" max="95"/>
-    <col width="329.1428571428572" customWidth="1" min="96" max="96"/>
-    <col width="329.1428571428572" customWidth="1" min="97" max="97"/>
-    <col width="329.1428571428572" customWidth="1" min="98" max="98"/>
-    <col width="329.1428571428572" customWidth="1" min="99" max="99"/>
-    <col width="329.1428571428572" customWidth="1" min="100" max="100"/>
-    <col width="329.1428571428572" customWidth="1" min="101" max="101"/>
-    <col width="329.1428571428572" customWidth="1" min="102" max="102"/>
-    <col width="329.1428571428572" customWidth="1" min="103" max="103"/>
-    <col width="329.1428571428572" customWidth="1" min="104" max="104"/>
-    <col width="329.1428571428572" customWidth="1" min="105" max="105"/>
-    <col width="329.1428571428572" customWidth="1" min="106" max="106"/>
-    <col width="329.1428571428572" customWidth="1" min="107" max="107"/>
-    <col width="329.1428571428572" customWidth="1" min="108" max="108"/>
-    <col width="329.1428571428572" customWidth="1" min="109" max="109"/>
-    <col width="329.1428571428572" customWidth="1" min="110" max="110"/>
-    <col width="329.1428571428572" customWidth="1" min="111" max="111"/>
-    <col width="329.1428571428572" customWidth="1" min="112" max="112"/>
-    <col width="329.1428571428572" customWidth="1" min="113" max="113"/>
-    <col width="329.1428571428572" customWidth="1" min="114" max="114"/>
-    <col width="329.1428571428572" customWidth="1" min="115" max="115"/>
-    <col width="329.1428571428572" customWidth="1" min="116" max="116"/>
-    <col width="329.1428571428572" customWidth="1" min="117" max="117"/>
-    <col width="329.1428571428572" customWidth="1" min="118" max="118"/>
-    <col width="329.1428571428572" customWidth="1" min="119" max="119"/>
-    <col width="329.1428571428572" customWidth="1" min="120" max="120"/>
-    <col width="329.1428571428572" customWidth="1" min="121" max="121"/>
-    <col width="329.1428571428572" customWidth="1" min="122" max="122"/>
-    <col width="329.1428571428572" customWidth="1" min="123" max="123"/>
-    <col width="329.1428571428572" customWidth="1" min="124" max="124"/>
-    <col width="329.1428571428572" customWidth="1" min="125" max="125"/>
-    <col width="329.1428571428572" customWidth="1" min="126" max="126"/>
-    <col width="329.1428571428572" customWidth="1" min="127" max="127"/>
-    <col width="329.1428571428572" customWidth="1" min="128" max="128"/>
-    <col width="329.1428571428572" customWidth="1" min="129" max="129"/>
-    <col width="329.1428571428572" customWidth="1" min="130" max="130"/>
-    <col width="329.1428571428572" customWidth="1" min="131" max="131"/>
-    <col width="329.1428571428572" customWidth="1" min="132" max="132"/>
-    <col width="329.1428571428572" customWidth="1" min="133" max="133"/>
-    <col width="329.1428571428572" customWidth="1" min="134" max="134"/>
-    <col width="329.1428571428572" customWidth="1" min="135" max="135"/>
-    <col width="329.1428571428572" customWidth="1" min="136" max="136"/>
-    <col width="329.1428571428572" customWidth="1" min="137" max="137"/>
-    <col width="329.1428571428572" customWidth="1" min="138" max="138"/>
-    <col width="329.1428571428572" customWidth="1" min="139" max="139"/>
-    <col width="329.1428571428572" customWidth="1" min="140" max="140"/>
-    <col width="329.1428571428572" customWidth="1" min="141" max="141"/>
-    <col width="329.1428571428572" customWidth="1" min="142" max="142"/>
-    <col width="329.1428571428572" customWidth="1" min="143" max="143"/>
-    <col width="329.1428571428572" customWidth="1" min="144" max="144"/>
-    <col width="329.1428571428572" customWidth="1" min="145" max="145"/>
-    <col width="329.1428571428572" customWidth="1" min="146" max="146"/>
-    <col width="329.1428571428572" customWidth="1" min="147" max="147"/>
-    <col width="329.1428571428572" customWidth="1" min="148" max="148"/>
-    <col width="329.1428571428572" customWidth="1" min="149" max="149"/>
-    <col width="329.1428571428572" customWidth="1" min="150" max="150"/>
-    <col width="329.1428571428572" customWidth="1" min="151" max="151"/>
-    <col width="329.1428571428572" customWidth="1" min="152" max="152"/>
-    <col width="329.1428571428572" customWidth="1" min="153" max="153"/>
-    <col width="329.1428571428572" customWidth="1" min="154" max="154"/>
-    <col width="329.1428571428572" customWidth="1" min="155" max="155"/>
-    <col width="329.1428571428572" customWidth="1" min="156" max="156"/>
-    <col width="329.1428571428572" customWidth="1" min="157" max="157"/>
-    <col width="329.1428571428572" customWidth="1" min="158" max="158"/>
-    <col width="329.1428571428572" customWidth="1" min="159" max="159"/>
-    <col width="329.1428571428572" customWidth="1" min="160" max="160"/>
-    <col width="329.1428571428572" customWidth="1" min="161" max="161"/>
-    <col width="329.1428571428572" customWidth="1" min="162" max="162"/>
-    <col width="329.1428571428572" customWidth="1" min="163" max="163"/>
-    <col width="329.1428571428572" customWidth="1" min="164" max="164"/>
-    <col width="329.1428571428572" customWidth="1" min="165" max="165"/>
-    <col width="329.1428571428572" customWidth="1" min="166" max="166"/>
-    <col width="329.1428571428572" customWidth="1" min="167" max="167"/>
-    <col width="329.1428571428572" customWidth="1" min="168" max="168"/>
-    <col width="329.1428571428572" customWidth="1" min="169" max="169"/>
-    <col width="329.1428571428572" customWidth="1" min="170" max="170"/>
-    <col width="329.1428571428572" customWidth="1" min="171" max="171"/>
-    <col width="329.1428571428572" customWidth="1" min="172" max="172"/>
-    <col width="329.1428571428572" customWidth="1" min="173" max="173"/>
-    <col width="329.1428571428572" customWidth="1" min="174" max="174"/>
-    <col width="329.1428571428572" customWidth="1" min="175" max="175"/>
-    <col width="329.1428571428572" customWidth="1" min="176" max="176"/>
-    <col width="329.1428571428572" customWidth="1" min="177" max="177"/>
-    <col width="329.1428571428572" customWidth="1" min="178" max="178"/>
-    <col width="329.1428571428572" customWidth="1" min="179" max="179"/>
-    <col width="329.1428571428572" customWidth="1" min="180" max="180"/>
-    <col width="329.1428571428572" customWidth="1" min="181" max="181"/>
-    <col width="329.1428571428572" customWidth="1" min="182" max="182"/>
-    <col width="329.1428571428572" customWidth="1" min="183" max="183"/>
-    <col width="329.1428571428572" customWidth="1" min="184" max="184"/>
-    <col width="329.1428571428572" customWidth="1" min="185" max="185"/>
-    <col width="329.1428571428572" customWidth="1" min="186" max="186"/>
-    <col width="329.1428571428572" customWidth="1" min="187" max="187"/>
-    <col width="329.1428571428572" customWidth="1" min="188" max="188"/>
-    <col width="329.1428571428572" customWidth="1" min="189" max="189"/>
-    <col width="329.1428571428572" customWidth="1" min="190" max="190"/>
-    <col width="329.1428571428572" customWidth="1" min="191" max="191"/>
-    <col width="329.1428571428572" customWidth="1" min="192" max="192"/>
-    <col width="329.1428571428572" customWidth="1" min="193" max="193"/>
-    <col width="329.1428571428572" customWidth="1" min="194" max="194"/>
-    <col width="329.1428571428572" customWidth="1" min="195" max="195"/>
-    <col width="329.1428571428572" customWidth="1" min="196" max="196"/>
-    <col width="329.1428571428572" customWidth="1" min="197" max="197"/>
-    <col width="329.1428571428572" customWidth="1" min="198" max="198"/>
-    <col width="329.1428571428572" customWidth="1" min="199" max="199"/>
-    <col width="329.1428571428572" customWidth="1" min="200" max="200"/>
-    <col width="329.1428571428572" customWidth="1" min="201" max="201"/>
-    <col width="329.1428571428572" customWidth="1" min="202" max="202"/>
-    <col width="329.1428571428572" customWidth="1" min="203" max="203"/>
-    <col width="329.1428571428572" customWidth="1" min="204" max="204"/>
-    <col width="329.1428571428572" customWidth="1" min="205" max="205"/>
-    <col width="329.1428571428572" customWidth="1" min="206" max="206"/>
-    <col width="329.1428571428572" customWidth="1" min="207" max="207"/>
-    <col width="329.1428571428572" customWidth="1" min="208" max="208"/>
-    <col width="329.1428571428572" customWidth="1" min="209" max="209"/>
-    <col width="329.1428571428572" customWidth="1" min="210" max="210"/>
-    <col width="329.1428571428572" customWidth="1" min="211" max="211"/>
-    <col width="329.1428571428572" customWidth="1" min="212" max="212"/>
-    <col width="329.1428571428572" customWidth="1" min="213" max="213"/>
-    <col width="329.1428571428572" customWidth="1" min="214" max="214"/>
-    <col width="329.1428571428572" customWidth="1" min="215" max="215"/>
-    <col width="329.1428571428572" customWidth="1" min="216" max="216"/>
-    <col width="329.1428571428572" customWidth="1" min="217" max="217"/>
-    <col width="329.1428571428572" customWidth="1" min="218" max="218"/>
-    <col width="329.1428571428572" customWidth="1" min="219" max="219"/>
-    <col width="329.1428571428572" customWidth="1" min="220" max="220"/>
-    <col width="329.1428571428572" customWidth="1" min="221" max="221"/>
-    <col width="329.1428571428572" customWidth="1" min="222" max="222"/>
-    <col width="329.1428571428572" customWidth="1" min="223" max="223"/>
-    <col width="329.1428571428572" customWidth="1" min="224" max="224"/>
-    <col width="329.1428571428572" customWidth="1" min="225" max="225"/>
-    <col width="329.1428571428572" customWidth="1" min="226" max="226"/>
-    <col width="329.1428571428572" customWidth="1" min="227" max="227"/>
-    <col width="329.1428571428572" customWidth="1" min="228" max="228"/>
-    <col width="329.1428571428572" customWidth="1" min="229" max="229"/>
-    <col width="329.1428571428572" customWidth="1" min="230" max="230"/>
-    <col width="329.1428571428572" customWidth="1" min="231" max="231"/>
-    <col width="329.1428571428572" customWidth="1" min="232" max="232"/>
-    <col width="329.1428571428572" customWidth="1" min="233" max="233"/>
-    <col width="329.1428571428572" customWidth="1" min="234" max="234"/>
-    <col width="329.1428571428572" customWidth="1" min="235" max="235"/>
-    <col width="329.1428571428572" customWidth="1" min="236" max="236"/>
-    <col width="329.1428571428572" customWidth="1" min="237" max="237"/>
-    <col width="329.1428571428572" customWidth="1" min="238" max="238"/>
-    <col width="329.1428571428572" customWidth="1" min="239" max="239"/>
-    <col width="329.1428571428572" customWidth="1" min="240" max="240"/>
-    <col width="329.1428571428572" customWidth="1" min="241" max="241"/>
-    <col width="329.1428571428572" customWidth="1" min="242" max="242"/>
-    <col width="329.1428571428572" customWidth="1" min="243" max="243"/>
-    <col width="329.1428571428572" customWidth="1" min="244" max="244"/>
-    <col width="329.1428571428572" customWidth="1" min="245" max="245"/>
-    <col width="329.1428571428572" customWidth="1" min="246" max="246"/>
-    <col width="329.1428571428572" customWidth="1" min="247" max="247"/>
-    <col width="329.1428571428572" customWidth="1" min="248" max="248"/>
-    <col width="329.1428571428572" customWidth="1" min="249" max="249"/>
-    <col width="329.1428571428572" customWidth="1" min="250" max="250"/>
-    <col width="329.1428571428572" customWidth="1" min="251" max="251"/>
-    <col width="329.1428571428572" customWidth="1" min="252" max="252"/>
-    <col width="329.1428571428572" customWidth="1" min="253" max="253"/>
-    <col width="329.1428571428572" customWidth="1" min="254" max="254"/>
-    <col width="329.1428571428572" customWidth="1" min="255" max="255"/>
-    <col width="329.1428571428572" customWidth="1" min="256" max="256"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2311,6 +2223,10 @@
           <t>增值税发票开票说明</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2325,6 +2241,10 @@
      A.取票人有效身份证件    B.INVOICE   C.客户信息采集表（首次开票的客户需提供，已备案的客户无需提供）</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2332,6 +2252,10 @@
           <t>客户信息采集表</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2339,6 +2263,10 @@
           <t>A. 以下资料为税票信息 （如果资料有更改，请务必及时通知）</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2346,6 +2274,10 @@
           <t>公司名称(中文全称):</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2353,6 +2285,10 @@
           <t>Company Name (English)：</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2360,6 +2296,10 @@
           <t>公司地址(中文)：</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2367,6 +2307,10 @@
           <t>Company Address (English)：</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2374,11 +2318,13 @@
           <t>邮编 (Postal code)：</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>电话：</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>传真：</t>
@@ -2391,6 +2337,10 @@
           <t>开户银行名称：</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2398,6 +2348,10 @@
           <t>开户银行账号：</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2405,6 +2359,10 @@
           <t>税务登记号：</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2412,6 +2370,9 @@
           <t>账单及电子税务发票接收邮箱：</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>联系人：</t>
@@ -2424,6 +2385,10 @@
           <t>增值税普通发票均为电子发票，电子发票将通过上述邮箱发送；增值税专用发票为纸质发票。</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2431,6 +2396,10 @@
           <t>纸质发票领取方式 (自取/快递)：</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2438,6 +2407,10 @@
           <t>B.以下资料为需要委托快递的客户填写</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2445,6 +2418,10 @@
           <t>收件公司名：</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2452,6 +2429,10 @@
           <t>收件地址：</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2459,6 +2440,10 @@
           <t>收件人及联系电话：</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2466,6 +2451,10 @@
           <t>我司承诺以上所提供的信息准确无误，请予以备案。</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2473,31 +2462,12 @@
           <t>签名盖章（公司公章）</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B5:F5"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>